--- a/docs/data/jp/xlsx/4765.xlsx
+++ b/docs/data/jp/xlsx/4765.xlsx
@@ -1156,7 +1156,7 @@
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>부문</t>
+          <t>자산운용 사업</t>
         </is>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -1436,7 +1436,7 @@
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>부문</t>
+          <t>금융서비스 사업</t>
         </is>
       </c>
       <c r="B10" s="10" t="n"/>
@@ -6532,7 +6532,7 @@
     <row r="90">
       <c r="A90" s="18" t="inlineStr">
         <is>
-          <t>Gain On Sale Of Crypto Assets NOI</t>
+          <t>암호자산 매각이익</t>
         </is>
       </c>
       <c r="F90" s="20" t="n">
@@ -6746,7 +6746,7 @@
     <row r="94">
       <c r="A94" s="18" t="inlineStr">
         <is>
-          <t>Amortization Of Stock Issuance Cost NOE</t>
+          <t>주식교부비 상각</t>
         </is>
       </c>
       <c r="C94" s="20" t="n">
@@ -6966,7 +6966,7 @@
     <row r="98">
       <c r="A98" s="18" t="inlineStr">
         <is>
-          <t>Gain On Redemption Of Investment Securities EI</t>
+          <t>투자유가증권 상환이익</t>
         </is>
       </c>
       <c r="H98" s="20" t="n">
@@ -7087,7 +7087,7 @@
     <row r="102">
       <c r="A102" s="18" t="inlineStr">
         <is>
-          <t>Loss On Valuation Of Crypto Assets</t>
+          <t>암호자산 평가손실</t>
         </is>
       </c>
       <c r="C102" s="20" t="n">
@@ -7128,7 +7128,7 @@
     <row r="104">
       <c r="A104" s="18" t="inlineStr">
         <is>
-          <t>Loss On Redemption Of Investment Securities EL</t>
+          <t>투자유가증권 상환손실</t>
         </is>
       </c>
       <c r="J104" s="20" t="n">
@@ -8406,7 +8406,7 @@
     <row r="128">
       <c r="A128" s="18" t="inlineStr">
         <is>
-          <t>부문 · 외부 고객 매출</t>
+          <t>자산운용 사업 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="C128" s="20" t="n">
@@ -8455,7 +8455,7 @@
     <row r="129">
       <c r="A129" s="18" t="inlineStr">
         <is>
-          <t>부문 · 외부 고객 매출</t>
+          <t>금융서비스 사업 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="C129" s="20" t="n">
@@ -8651,7 +8651,7 @@
     <row r="133">
       <c r="A133" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 간 내부매출·대체</t>
+          <t>자산운용 사업 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C133" s="20" t="n">
@@ -8700,7 +8700,7 @@
     <row r="134">
       <c r="A134" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 간 내부매출·대체</t>
+          <t>금융서비스 사업 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C134" s="20" t="n">
@@ -8896,7 +8896,7 @@
     <row r="138">
       <c r="A138" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>자산운용 사업 · 계</t>
         </is>
       </c>
       <c r="C138" s="20" t="n">
@@ -8945,7 +8945,7 @@
     <row r="139">
       <c r="A139" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>금융서비스 사업 · 계</t>
         </is>
       </c>
       <c r="C139" s="20" t="n">
@@ -9141,7 +9141,7 @@
     <row r="143">
       <c r="A143" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익</t>
+          <t>자산운용 사업 · 부문 이익</t>
         </is>
       </c>
       <c r="C143" s="20" t="n">
@@ -9190,7 +9190,7 @@
     <row r="144">
       <c r="A144" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익</t>
+          <t>금융서비스 사업 · 부문 이익</t>
         </is>
       </c>
       <c r="C144" s="20" t="n">
@@ -9682,7 +9682,7 @@
     <row r="153">
       <c r="A153" s="18" t="inlineStr">
         <is>
-          <t>Amortization Of Long Term Prepaid Expenses Ope CF</t>
+          <t>장기선급비용 상각액</t>
         </is>
       </c>
       <c r="C153" s="20" t="n">
@@ -9821,7 +9821,7 @@
     <row r="157">
       <c r="A157" s="18" t="inlineStr">
         <is>
-          <t>Amortization Of Stock Issuance Cost Ope CF</t>
+          <t>주식교부비 상각</t>
         </is>
       </c>
       <c r="C157" s="20" t="n">
@@ -10012,7 +10012,7 @@
     <row r="162">
       <c r="A162" s="18" t="inlineStr">
         <is>
-          <t>Loss Gain On Transfer Of Business Ope CF</t>
+          <t>사업양도 손익</t>
         </is>
       </c>
       <c r="O162" s="20" t="n">
@@ -10025,7 +10025,7 @@
     <row r="163">
       <c r="A163" s="18" t="inlineStr">
         <is>
-          <t>Gain On Investments In Held In Trust Ope CF</t>
+          <t>신탁운용이익</t>
         </is>
       </c>
       <c r="O163" s="20" t="n">
@@ -10038,7 +10038,7 @@
     <row r="164">
       <c r="A164" s="18" t="inlineStr">
         <is>
-          <t>Relocation Expenses Ope CF</t>
+          <t>이전비용</t>
         </is>
       </c>
       <c r="P164" s="20" t="n">
@@ -10110,7 +10110,7 @@
     <row r="167">
       <c r="A167" s="18" t="inlineStr">
         <is>
-          <t>Loss On Crypto Assets</t>
+          <t>암호자산 평가손실</t>
         </is>
       </c>
       <c r="T167" s="20" t="n">
@@ -10123,7 +10123,7 @@
     <row r="168">
       <c r="A168" s="18" t="inlineStr">
         <is>
-          <t>Loss On Crypto Assets Ope CF</t>
+          <t>암호자산 평가손실</t>
         </is>
       </c>
       <c r="E168" s="20" t="n">
@@ -10139,7 +10139,7 @@
     <row r="169">
       <c r="A169" s="18" t="inlineStr">
         <is>
-          <t>Loss Gain On Sale Of Cryptocurrency Ope CF</t>
+          <t>암호자산 매각손익</t>
         </is>
       </c>
       <c r="G169" s="20" t="n">
@@ -10152,7 +10152,7 @@
     <row r="170">
       <c r="A170" s="18" t="inlineStr">
         <is>
-          <t>Loss Gain On Sale Of Crypto Assets Ope CF</t>
+          <t>암호자산 매각손익</t>
         </is>
       </c>
       <c r="E170" s="20" t="n">
@@ -10180,7 +10180,7 @@
     <row r="171">
       <c r="A171" s="18" t="inlineStr">
         <is>
-          <t>Loss On Retirement Of Intangible Assets Ope CF</t>
+          <t>무형자산 제각손실</t>
         </is>
       </c>
       <c r="E171" s="20" t="n">
@@ -10258,7 +10258,7 @@
     <row r="174">
       <c r="A174" s="18" t="inlineStr">
         <is>
-          <t>Loss On Reorganizaiton</t>
+          <t>조직재편비용</t>
         </is>
       </c>
       <c r="T174" s="20" t="n">
@@ -10271,7 +10271,7 @@
     <row r="175">
       <c r="A175" s="18" t="inlineStr">
         <is>
-          <t>Refund Of Right Of Use Brand License</t>
+          <t>브랜드 반환 수입</t>
         </is>
       </c>
       <c r="T175" s="20" t="n">
@@ -10284,7 +10284,7 @@
     <row r="176">
       <c r="A176" s="18" t="inlineStr">
         <is>
-          <t>Loss On Reorganizaiton Ope CF</t>
+          <t>조직재편비용</t>
         </is>
       </c>
       <c r="E176" s="20" t="n">
@@ -10300,7 +10300,7 @@
     <row r="177">
       <c r="A177" s="18" t="inlineStr">
         <is>
-          <t>Refund Of Right Of Use Brand License Ope CF</t>
+          <t>브랜드 반환 수입</t>
         </is>
       </c>
       <c r="E177" s="20" t="n">
@@ -10586,7 +10586,7 @@
     <row r="184">
       <c r="A184" s="18" t="inlineStr">
         <is>
-          <t>Decrease Increase In Investment Securities For Sale Ope CF</t>
+          <t>영업투자유가증권 증감액</t>
         </is>
       </c>
       <c r="I184" s="20" t="n">
@@ -11445,7 +11445,7 @@
     <row r="203">
       <c r="A203" s="18" t="inlineStr">
         <is>
-          <t>Payment For Liquidation Of Subsidiaries</t>
+          <t>자회사 청산 지출</t>
         </is>
       </c>
       <c r="P203" s="20" t="n">
@@ -11585,7 +11585,7 @@
     <row r="208">
       <c r="A208" s="18" t="inlineStr">
         <is>
-          <t>Proceeds From Transfer Of Business Inv CF</t>
+          <t>사업양도 수입</t>
         </is>
       </c>
       <c r="O208" s="20" t="n">
@@ -11653,7 +11653,7 @@
     <row r="210">
       <c r="A210" s="18" t="inlineStr">
         <is>
-          <t>Proceeds From Exercise Of Stock Option Fin CF</t>
+          <t>스톡옵션 행사 수입</t>
         </is>
       </c>
       <c r="O210" s="20" t="n">
@@ -11902,7 +11902,7 @@
     <row r="219">
       <c r="A219" s="18" t="inlineStr">
         <is>
-          <t>Proceeds From Changes In Ownership Interests In Subsidiaries That Do Not Result In Change In Scope Of Consolidation Fin CF</t>
+          <t>연결범위 변동 없는 자회사 주식 매각 수입</t>
         </is>
       </c>
       <c r="Q219" s="20" t="n">
@@ -12178,7 +12178,7 @@
     <row r="225">
       <c r="A225" s="18" t="inlineStr">
         <is>
-          <t>Increase In Cash And Cash Equivalents Due To Simplified Partial Share Exchange CCE</t>
+          <t>주식교부에 따른 현금성자산 증가액</t>
         </is>
       </c>
       <c r="G225" s="20" t="n">
@@ -15100,7 +15100,7 @@
     <row r="76">
       <c r="A76" s="18" t="inlineStr">
         <is>
-          <t>Operational Investment Securities CA</t>
+          <t>영업투자유가증권</t>
         </is>
       </c>
       <c r="E76" s="20" t="n">
@@ -15122,7 +15122,7 @@
     <row r="77">
       <c r="A77" s="18" t="inlineStr">
         <is>
-          <t>Cash Segregated As Deposits For Customers CASEC</t>
+          <t>고객 분별금 신탁</t>
         </is>
       </c>
       <c r="E77" s="20" t="n">
@@ -15292,7 +15292,7 @@
     <row r="82">
       <c r="A82" s="18" t="inlineStr">
         <is>
-          <t>Buildings And Accompanying Facilities Net</t>
+          <t>건물부속설비(순액)</t>
         </is>
       </c>
       <c r="C82" s="20" t="n">
@@ -16319,7 +16319,7 @@
     <row r="113">
       <c r="A113" s="18" t="inlineStr">
         <is>
-          <t>Long Term Lease Obligations NCL</t>
+          <t>장기 리스부채</t>
         </is>
       </c>
       <c r="H113" s="20" t="n">
